--- a/artfynd/A 40469-2024 artfynd.xlsx
+++ b/artfynd/A 40469-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120428564</v>
+        <v>120428522</v>
       </c>
       <c r="B2" t="n">
-        <v>74640</v>
+        <v>74638</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>306</v>
+        <v>6439</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120428517</v>
+        <v>120428380</v>
       </c>
       <c r="B3" t="n">
-        <v>74646</v>
+        <v>91200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,14 +820,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>NO Gräskärret, Ög</t>
+          <t>Pettersberg, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537690</v>
+        <v>537576</v>
       </c>
       <c r="R3" t="n">
-        <v>6493743</v>
+        <v>6493788</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120428522</v>
+        <v>120428564</v>
       </c>
       <c r="B4" t="n">
-        <v>74638</v>
+        <v>74640</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6439</v>
+        <v>306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120428380</v>
+        <v>120428517</v>
       </c>
       <c r="B5" t="n">
-        <v>91200</v>
+        <v>74646</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1339</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1032,14 +1032,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pettersberg, Ög</t>
+          <t>NO Gräskärret, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>537576</v>
+        <v>537690</v>
       </c>
       <c r="R5" t="n">
-        <v>6493788</v>
+        <v>6493743</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 40469-2024 artfynd.xlsx
+++ b/artfynd/A 40469-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120428522</v>
+        <v>120428380</v>
       </c>
       <c r="B2" t="n">
-        <v>74638</v>
+        <v>91200</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6439</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>NO Gräskärret, Ög</t>
+          <t>Pettersberg, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537690</v>
+        <v>537576</v>
       </c>
       <c r="R2" t="n">
-        <v>6493743</v>
+        <v>6493788</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120428380</v>
+        <v>120428522</v>
       </c>
       <c r="B3" t="n">
-        <v>91200</v>
+        <v>74638</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>6439</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,14 +820,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pettersberg, Ög</t>
+          <t>NO Gräskärret, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537576</v>
+        <v>537690</v>
       </c>
       <c r="R3" t="n">
-        <v>6493788</v>
+        <v>6493743</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>

--- a/artfynd/A 40469-2024 artfynd.xlsx
+++ b/artfynd/A 40469-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120428380</v>
+        <v>120428517</v>
       </c>
       <c r="B2" t="n">
-        <v>91200</v>
+        <v>74646</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pettersberg, Ög</t>
+          <t>NO Gräskärret, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537576</v>
+        <v>537690</v>
       </c>
       <c r="R2" t="n">
-        <v>6493788</v>
+        <v>6493743</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120428522</v>
+        <v>120428380</v>
       </c>
       <c r="B3" t="n">
-        <v>74638</v>
+        <v>91200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6439</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,14 +820,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>NO Gräskärret, Ög</t>
+          <t>Pettersberg, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537690</v>
+        <v>537576</v>
       </c>
       <c r="R3" t="n">
-        <v>6493743</v>
+        <v>6493788</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120428517</v>
+        <v>120428522</v>
       </c>
       <c r="B5" t="n">
-        <v>74646</v>
+        <v>74638</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 40469-2024 artfynd.xlsx
+++ b/artfynd/A 40469-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120428380</v>
+        <v>120428522</v>
       </c>
       <c r="B3" t="n">
-        <v>91200</v>
+        <v>74638</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>6439</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,14 +820,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pettersberg, Ög</t>
+          <t>NO Gräskärret, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537576</v>
+        <v>537690</v>
       </c>
       <c r="R3" t="n">
-        <v>6493788</v>
+        <v>6493743</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120428522</v>
+        <v>120428380</v>
       </c>
       <c r="B5" t="n">
-        <v>74638</v>
+        <v>91200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>1339</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1032,14 +1032,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>NO Gräskärret, Ög</t>
+          <t>Pettersberg, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>537690</v>
+        <v>537576</v>
       </c>
       <c r="R5" t="n">
-        <v>6493743</v>
+        <v>6493788</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 40469-2024 artfynd.xlsx
+++ b/artfynd/A 40469-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120428517</v>
+        <v>120428564</v>
       </c>
       <c r="B2" t="n">
-        <v>74646</v>
+        <v>74640</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120428522</v>
+        <v>120428380</v>
       </c>
       <c r="B3" t="n">
-        <v>74638</v>
+        <v>91200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6439</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,14 +820,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>NO Gräskärret, Ög</t>
+          <t>Pettersberg, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537690</v>
+        <v>537576</v>
       </c>
       <c r="R3" t="n">
-        <v>6493743</v>
+        <v>6493788</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120428564</v>
+        <v>120428517</v>
       </c>
       <c r="B4" t="n">
-        <v>74640</v>
+        <v>74646</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120428380</v>
+        <v>120428522</v>
       </c>
       <c r="B5" t="n">
-        <v>91200</v>
+        <v>74638</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1339</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1032,14 +1032,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pettersberg, Ög</t>
+          <t>NO Gräskärret, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>537576</v>
+        <v>537690</v>
       </c>
       <c r="R5" t="n">
-        <v>6493788</v>
+        <v>6493743</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 40469-2024 artfynd.xlsx
+++ b/artfynd/A 40469-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120428564</v>
+        <v>120428380</v>
       </c>
       <c r="B2" t="n">
-        <v>74640</v>
+        <v>91200</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>306</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>NO Gräskärret, Ög</t>
+          <t>Pettersberg, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537690</v>
+        <v>537576</v>
       </c>
       <c r="R2" t="n">
-        <v>6493743</v>
+        <v>6493788</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120428380</v>
+        <v>120428564</v>
       </c>
       <c r="B3" t="n">
-        <v>91200</v>
+        <v>74640</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,14 +820,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pettersberg, Ög</t>
+          <t>NO Gräskärret, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537576</v>
+        <v>537690</v>
       </c>
       <c r="R3" t="n">
-        <v>6493788</v>
+        <v>6493743</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>

--- a/artfynd/A 40469-2024 artfynd.xlsx
+++ b/artfynd/A 40469-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120428380</v>
+        <v>120428564</v>
       </c>
       <c r="B2" t="n">
-        <v>91264</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +709,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pettersberg, Ög</t>
+          <t>NO Gräskärret, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537576</v>
+        <v>537690</v>
       </c>
       <c r="R2" t="n">
-        <v>6493788</v>
+        <v>6493743</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120428522</v>
+        <v>120428517</v>
       </c>
       <c r="B3" t="n">
-        <v>74658</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6439</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -887,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120428517</v>
+        <v>120428380</v>
       </c>
       <c r="B4" t="n">
-        <v>74666</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -926,14 +911,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>NO Gräskärret, Ög</t>
+          <t>Pettersberg, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537690</v>
+        <v>537576</v>
       </c>
       <c r="R4" t="n">
-        <v>6493743</v>
+        <v>6493788</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120428564</v>
+        <v>120428522</v>
       </c>
       <c r="B5" t="n">
-        <v>74660</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>306</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 40469-2024 artfynd.xlsx
+++ b/artfynd/A 40469-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120428564</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120428517</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120428380</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,8 +1096,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120428522</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>